--- a/Groceryapptesting/src/test/resources/Testdata.xlsx
+++ b/Groceryapptesting/src/test/resources/Testdata.xlsx
@@ -70,7 +70,7 @@
     <t>Dropdown</t>
   </si>
   <si>
-    <t>RiyaRoyRiya</t>
+    <t>Athirasdf</t>
   </si>
   <si>
     <t>Iri!!!234</t>
@@ -82,7 +82,7 @@
     <t>CategoryName</t>
   </si>
   <si>
-    <t>Groceries and Food Supply</t>
+    <t>Petstation</t>
   </si>
   <si>
     <t>Address</t>

--- a/Groceryapptesting/src/test/resources/Testdata.xlsx
+++ b/Groceryapptesting/src/test/resources/Testdata.xlsx
@@ -70,7 +70,7 @@
     <t>Dropdown</t>
   </si>
   <si>
-    <t>Athirasdf</t>
+    <t>Sheethal VN</t>
   </si>
   <si>
     <t>Iri!!!234</t>
@@ -82,7 +82,7 @@
     <t>CategoryName</t>
   </si>
   <si>
-    <t>Petstation</t>
+    <t>ZooM</t>
   </si>
   <si>
     <t>Address</t>
@@ -94,7 +94,7 @@
     <t>Phone</t>
   </si>
   <si>
-    <t>Abc,Town,NorthAmerica</t>
+    <t>sdf,Town,NorthAmerica,usa</t>
   </si>
   <si>
     <t>xyz@yahoo.com</t>
@@ -1421,7 +1421,7 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="14.2222222222222"/>
+    <col min="1" max="1" width="18.7777777777778"/>
     <col min="2" max="2" width="18.4444444444444" customWidth="1"/>
     <col min="4" max="5" width="13.5555555555556" customWidth="1"/>
   </cols>
@@ -1445,7 +1445,7 @@
     </row>
     <row r="2" ht="13.8" spans="1:5">
       <c r="A2" s="1">
-        <v>423345678</v>
+        <v>42141241</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>25</v>

--- a/Groceryapptesting/src/test/resources/Testdata.xlsx
+++ b/Groceryapptesting/src/test/resources/Testdata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400" activeTab="5"/>
+    <workbookView windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="LoginPage" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
     <t>Dropdown</t>
   </si>
   <si>
-    <t>Sheethal VN</t>
+    <t>AmeyaSreyus</t>
   </si>
   <si>
     <t>Iri!!!234</t>
@@ -82,7 +82,7 @@
     <t>CategoryName</t>
   </si>
   <si>
-    <t>ZooM</t>
+    <t>Cartridge</t>
   </si>
   <si>
     <t>Address</t>

--- a/Groceryapptesting/src/test/resources/Testdata.xlsx
+++ b/Groceryapptesting/src/test/resources/Testdata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="8400" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="LoginPage" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
     <t>Dropdown</t>
   </si>
   <si>
-    <t>AmeyaSreyus</t>
+    <t>Ananyas</t>
   </si>
   <si>
     <t>Iri!!!234</t>

--- a/Groceryapptesting/src/test/resources/Testdata.xlsx
+++ b/Groceryapptesting/src/test/resources/Testdata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="8400" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="LoginPage" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
     <t>Dropdown</t>
   </si>
   <si>
-    <t>Ananyas</t>
+    <t>Veena PMS</t>
   </si>
   <si>
     <t>Iri!!!234</t>
@@ -82,7 +82,7 @@
     <t>CategoryName</t>
   </si>
   <si>
-    <t>Cartridge</t>
+    <t>Sunrise1</t>
   </si>
   <si>
     <t>Address</t>

--- a/Groceryapptesting/src/test/resources/Testdata.xlsx
+++ b/Groceryapptesting/src/test/resources/Testdata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="8400" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="LoginPage" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
     <t>Dropdown</t>
   </si>
   <si>
-    <t>Veena PMS</t>
+    <t>AnvithaAnoop</t>
   </si>
   <si>
     <t>Iri!!!234</t>
@@ -82,7 +82,7 @@
     <t>CategoryName</t>
   </si>
   <si>
-    <t>Sunrise1</t>
+    <t>Signature Rise</t>
   </si>
   <si>
     <t>Address</t>
@@ -769,7 +769,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="C1" s="6"/>
     </row>
-    <row r="2" customHeight="1" spans="1:2">
+    <row r="2" customHeight="1" spans="1:3">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:2">
+    <row r="3" customHeight="1" spans="1:3">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:2">
+    <row r="4" customHeight="1" spans="1:3">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:2">
+    <row r="5" customHeight="1" spans="1:3">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
